--- a/output/full_scan/batch_seq5_2026-07-27.xlsx
+++ b/output/full_scan/batch_seq5_2026-07-27.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O219"/>
+  <dimension ref="A1:O226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6134</v>
+        <v>5533</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>萬旭</t>
+          <t>皇鼎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>416.1864164430184</v>
+        <v>416.6304874079819</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>27.35</v>
+        <v>14.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>36.88039773501978</v>
+        <v>62.68161165865271</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.458009387144</v>
+        <v>18.68869832428411</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3233674775649633</v>
+        <v>0.5878072290402024</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2394322114863176</v>
+        <v>0.0538201567934251</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>rsi_strong, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4557</v>
+        <v>6134</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>永新-KY</t>
+          <t>萬旭</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>416.1831197360282</v>
+        <v>416.1864164430184</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>51.8</v>
+        <v>27.35</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>58.55671259199992</v>
+        <v>36.88039773501978</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.31802955107589</v>
+        <v>29.458009387144</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5099026460212445</v>
+        <v>0.3233674775649633</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2112425034662542</v>
+        <v>-0.2394322114863176</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>5481</v>
+        <v>4557</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>永新-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>415.8416858789858</v>
+        <v>416.1831197360282</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20.85</v>
+        <v>51.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.96264068071139</v>
+        <v>58.55671259199992</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.17550677715767</v>
+        <v>28.31802955107589</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6157044978159312</v>
+        <v>0.5099026460212445</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0163547231568689</v>
+        <v>0.2112425034662542</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>5452</v>
+        <v>5481</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>佶優</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>412.9288803472239</v>
+        <v>415.8416858789858</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>26.1</v>
+        <v>20.85</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>32.477887547528</v>
+        <v>48.96264068071139</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.32763653229501</v>
+        <v>21.17550677715767</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1678388532496838</v>
+        <v>0.6157044978159312</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.4221070424611071</v>
+        <v>-0.0163547231568689</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6154</v>
+        <v>5452</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>順發</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>409.7777902138818</v>
+        <v>412.9288803472239</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13.8</v>
+        <v>26.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.52502387257869</v>
+        <v>32.477887547528</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.08972671499807</v>
+        <v>24.32763653229501</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.122403898536556</v>
+        <v>0.1678388532496838</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>1</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0107841122767799</v>
+        <v>-0.4221070424611071</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>5489</v>
+        <v>6154</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>順發</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>406.8375868041649</v>
+        <v>409.7777902138818</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>44.95</v>
+        <v>13.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.15042188598591</v>
+        <v>53.52502387257869</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>31.27025357047193</v>
+        <v>12.08972671499807</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3104180134545959</v>
+        <v>2.122403898536556</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.823804771384077</v>
+        <v>-0.0107841122767799</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>5460</v>
+        <v>5489</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>405.4966752658369</v>
+        <v>406.8375868041649</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15.95</v>
+        <v>44.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.05373215896962</v>
+        <v>39.15042188598591</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>38.03990452496271</v>
+        <v>31.27025357047193</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.0891927554677119</v>
+        <v>0.3104180134545959</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>2</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1865926249510177</v>
+        <v>-1.823804771384077</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6127</v>
+        <v>5460</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>九豪</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>404.4377707832834</v>
+        <v>405.4966752658369</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>53.3</v>
+        <v>15.95</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>33.24526783572996</v>
+        <v>45.05373215896962</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>33.55677517775816</v>
+        <v>38.03990452496271</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4193823915541994</v>
+        <v>0.0891927554677119</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.69344951847884</v>
+        <v>-0.1865926249510177</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>5439</v>
+        <v>6127</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>九豪</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>402.528676569805</v>
+        <v>404.4377707832834</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>234</v>
+        <v>53.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>25.48443585149475</v>
+        <v>33.24526783572996</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>30.52764162003266</v>
+        <v>33.55677517775816</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9499345635041432</v>
+        <v>0.4193823915541994</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-6.040804117429321</v>
+        <v>-2.69344951847884</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>4766</v>
+        <v>5439</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>399.0066769144639</v>
+        <v>402.528676569805</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>328.5</v>
+        <v>234</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>38.05962095857625</v>
+        <v>25.48443585149475</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.35938257696986</v>
+        <v>30.52764162003266</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4586379223834835</v>
+        <v>0.9499345635041432</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.9008463139653921</v>
+        <v>-6.040804117429321</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>5536</v>
+        <v>4766</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>396.6552902780971</v>
+        <v>399.0066769144639</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1105</v>
+        <v>328.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,49 +4050,49 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.56265901783125</v>
+        <v>38.05962095857625</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.48360488152039</v>
+        <v>21.35938257696986</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7831525564223033</v>
+        <v>0.4586379223834835</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-24.59956859740551</v>
+        <v>-0.9008463139653921</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>4930</v>
+        <v>5536</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>395.6772947691426</v>
+        <v>396.6552902780971</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>16.35</v>
+        <v>1105</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>32.81931756341977</v>
+        <v>41.56265901783125</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.03616190803754</v>
+        <v>19.48360488152039</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.059483817573402</v>
+        <v>0.7831525564223033</v>
       </c>
       <c r="K69" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0398973004977073</v>
+        <v>-24.59956859740551</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>5340</v>
+        <v>5522</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>394.2448811004315</v>
+        <v>396.403465252127</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>31.4765846482621</v>
+        <v>45.17184730971021</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.96384725992633</v>
+        <v>15.80952515912502</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7036365428431076</v>
+        <v>0.2821696903785903</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.6941257593686565</v>
+        <v>0.2384427297645861</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>4949</v>
+        <v>4930</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>390.8722870912511</v>
+        <v>395.6772947691426</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>66.5</v>
+        <v>16.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>33.53874071714932</v>
+        <v>32.81931756341977</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.58975288598315</v>
+        <v>20.03616190803754</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4034658436663293</v>
+        <v>2.059483817573402</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4321088066553917</v>
+        <v>-0.0398973004977073</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6136</v>
+        <v>5340</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>390.345066180797</v>
+        <v>394.2448811004315</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>24.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.9485259169054</v>
+        <v>31.4765846482621</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.0857299327326</v>
+        <v>27.96384725992633</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5644315241851195</v>
+        <v>0.7036365428431076</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0535696851832628</v>
+        <v>-0.6941257593686565</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>5348</v>
+        <v>4949</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>387.5403446645993</v>
+        <v>390.8722870912511</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>16.5</v>
+        <v>66.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.6185672851103</v>
+        <v>33.53874071714932</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5.739325337609047</v>
+        <v>23.58975288598315</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5409025690858746</v>
+        <v>0.4034658436663293</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1069668902801116</v>
+        <v>-0.4321088066553917</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>5484</v>
+        <v>6136</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>385.4430098613813</v>
+        <v>390.345066180797</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.15</v>
+        <v>24.4</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.46982359774052</v>
+        <v>44.9485259169054</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.40467595471378</v>
+        <v>24.0857299327326</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4945257645214069</v>
+        <v>0.5644315241851195</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6825441568655095</v>
+        <v>0.0535696851832628</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>4755</v>
+        <v>5348</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>384.8392055591227</v>
+        <v>387.5403446645993</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>115</v>
+        <v>16.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.96801149376131</v>
+        <v>51.6185672851103</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.77461742799409</v>
+        <v>5.739325337609047</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7231379592589314</v>
+        <v>0.5409025690858746</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.505148726688851</v>
+        <v>-0.1069668902801116</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6153</v>
+        <v>5484</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>384.2638811461096</v>
+        <v>385.4430098613813</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.1</v>
+        <v>40.15</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>30.64365783530862</v>
+        <v>36.46982359774052</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>34.6490552717034</v>
+        <v>16.40467595471378</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7105147004814218</v>
+        <v>0.4945257645214069</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.318651343281821</v>
+        <v>-0.6825441568655095</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>4927</v>
+        <v>4755</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>382.4598159135535</v>
+        <v>384.8392055591227</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>34.1</v>
+        <v>115</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27.2099759340956</v>
+        <v>34.96801149376131</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>33.31876703500224</v>
+        <v>15.77461742799409</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4735845305308409</v>
+        <v>0.7231379592589314</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.3863705115162199</v>
+        <v>-1.505148726688851</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6155</v>
+        <v>6153</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>382.1127337971098</v>
+        <v>384.2638811461096</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>55</v>
+        <v>16.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>30.28725467216485</v>
+        <v>30.64365783530862</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>28.62506054117731</v>
+        <v>34.6490552717034</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3645917152069566</v>
+        <v>0.7105147004814218</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-2.213935689288127</v>
+        <v>-0.318651343281821</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>4763</v>
+        <v>4927</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>380.8701448879095</v>
+        <v>382.4598159135535</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>49.7</v>
+        <v>34.1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>57.02741867737456</v>
+        <v>27.2099759340956</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.18366475043315</v>
+        <v>33.31876703500224</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5347539544606706</v>
+        <v>0.4735845305308409</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.09701047280717499</v>
+        <v>-0.3863705115162199</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>4720</v>
+        <v>6155</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>德淵</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>379.9337747283039</v>
+        <v>382.1127337971098</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>19.55</v>
+        <v>55</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>31.45648305585038</v>
+        <v>30.28725467216485</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22.00221680479955</v>
+        <v>28.62506054117731</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.1552555605413579</v>
+        <v>0.3645917152069566</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3021312100940743</v>
+        <v>-2.213935689288127</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>5291</v>
+        <v>4763</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>379.3935607699762</v>
+        <v>380.8701448879095</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>51.2</v>
+        <v>49.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>38.77229954387403</v>
+        <v>57.02741867737456</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.04790368072801</v>
+        <v>20.18366475043315</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7540905223468766</v>
+        <v>0.5347539544606706</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2142217390357426</v>
+        <v>0.09701047280717499</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>4582</v>
+        <v>4720</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>德淵</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>377.554207340267</v>
+        <v>379.9337747283039</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>27.95</v>
+        <v>19.55</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.39459063876225</v>
+        <v>31.45648305585038</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.86762640904663</v>
+        <v>22.00221680479955</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7388013595538486</v>
+        <v>0.1552555605413579</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1934852797771877</v>
+        <v>-0.3021312100940743</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>5284</v>
+        <v>5291</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>jpp-KY</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>377.4058341246461</v>
+        <v>379.3935607699762</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>285</v>
+        <v>51.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>30.58502907295932</v>
+        <v>38.77229954387403</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.55480876638583</v>
+        <v>24.04790368072801</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3097732501446453</v>
+        <v>0.7540905223468766</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.282641853204272</v>
+        <v>0.2142217390357426</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6142</v>
+        <v>4582</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>友勁</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>375.3897359354079</v>
+        <v>377.554207340267</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>10.45</v>
+        <v>27.95</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>58.63674899779367</v>
+        <v>54.39459063876225</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>30.01787488079931</v>
+        <v>17.86762640904663</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.28238703107954</v>
+        <v>0.7388013595538486</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0295979996491178</v>
+        <v>0.1934852797771877</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6163</v>
+        <v>5284</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>jpp-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>375.3326736423798</v>
+        <v>377.4058341246461</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>41</v>
+        <v>285</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>37.75250729609962</v>
+        <v>30.58502907295932</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>35.11936224063478</v>
+        <v>29.55480876638583</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9028667896715302</v>
+        <v>0.3097732501446453</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>1</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1029586510685356</v>
+        <v>-2.282641853204272</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>5309</v>
+        <v>6142</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>友勁</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>375.0787631748563</v>
+        <v>375.3897359354079</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>52.6</v>
+        <v>10.45</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>31.09125898741709</v>
+        <v>58.63674899779367</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.97488330720441</v>
+        <v>30.01787488079931</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3297015115809785</v>
+        <v>1.28238703107954</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.6450132354551008</v>
+        <v>-0.0295979996491178</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>4919</v>
+        <v>6163</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>368.5938262878447</v>
+        <v>375.3326736423798</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>132.5</v>
+        <v>41</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>35.91511579158326</v>
+        <v>37.75250729609962</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.41534541327812</v>
+        <v>35.11936224063478</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6282174890536256</v>
+        <v>0.9028667896715302</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.653124146995584</v>
+        <v>-0.1029586510685356</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>4956</v>
+        <v>5309</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>368.2306517440649</v>
+        <v>375.0787631748563</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>29.15</v>
+        <v>52.6</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>31.14257978791619</v>
+        <v>31.09125898741709</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.34531472366656</v>
+        <v>27.97488330720441</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3592408745984273</v>
+        <v>0.3297015115809785</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.3222223002167124</v>
+        <v>-0.6450132354551008</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>5490</v>
+        <v>4919</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>367.6935955399115</v>
+        <v>368.5938262878447</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>32.7</v>
+        <v>132.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>62.13540671669622</v>
+        <v>35.91511579158326</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>24.12941937099212</v>
+        <v>20.41534541327812</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6917512744484934</v>
+        <v>0.6282174890536256</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.3083380762694712</v>
+        <v>-2.653124146995584</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>4771</v>
+        <v>4956</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>望隼</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>366.4778225442959</v>
+        <v>368.2306517440649</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>187.5</v>
+        <v>29.15</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>38.54788522937835</v>
+        <v>31.14257978791619</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.44401670611203</v>
+        <v>23.34531472366656</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4131213835826082</v>
+        <v>0.3592408745984273</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-2.550907013912456</v>
+        <v>-0.3222223002167124</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>5243</v>
+        <v>5490</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>366.1895890763197</v>
+        <v>367.6935955399115</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>86.5</v>
+        <v>32.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>35.04703426186667</v>
+        <v>62.13540671669622</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>24.01861682338668</v>
+        <v>24.12941937099212</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5679586923575224</v>
+        <v>0.6917512744484934</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.4996914084602863</v>
+        <v>0.3083380762694712</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>5314</v>
+        <v>4771</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>望隼</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>364.4551415079953</v>
+        <v>366.4778225442959</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>56.7</v>
+        <v>187.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.49582024968565</v>
+        <v>38.54788522937835</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.83594793423405</v>
+        <v>21.44401670611203</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.1903236089798984</v>
+        <v>0.4131213835826082</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.036244892384858</v>
+        <v>-2.550907013912456</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6103</v>
+        <v>5243</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>362</v>
+        <v>366.1895890763197</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>33.1</v>
+        <v>86.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.41783222278331</v>
+        <v>35.04703426186667</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.346724778782898</v>
+        <v>24.01861682338668</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>11.32143988176924</v>
+        <v>0.5679586923575224</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.7815765263744024</v>
+        <v>-0.4996914084602863</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>5487</v>
+        <v>5314</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>359.70215383088</v>
+        <v>364.4551415079953</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>28.15</v>
+        <v>56.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.07775279706613</v>
+        <v>41.49582024968565</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>32.08081810343347</v>
+        <v>14.83594793423405</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8041847638137595</v>
+        <v>0.1903236089798984</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0448150796390798</v>
+        <v>-1.036244892384858</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4540</v>
+        <v>6103</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>全球傳動</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>359.2716887303256</v>
+        <v>362</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>51</v>
+        <v>33.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.37738803334754</v>
+        <v>52.41783222278331</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.6515066601537</v>
+        <v>6.346724778782898</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2888889938954439</v>
+        <v>11.32143988176924</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.406700310518187</v>
+        <v>0.7815765263744024</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6108</v>
+        <v>5487</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>359.1587650020796</v>
+        <v>359.70215383088</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>16.9</v>
+        <v>28.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.11834371386737</v>
+        <v>49.07775279706613</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.91953477863228</v>
+        <v>32.08081810343347</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9009318776174722</v>
+        <v>0.8041847638137595</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0727892752718297</v>
+        <v>-0.0448150796390798</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>4972</v>
+        <v>4540</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>全球傳動</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>352.6943077243739</v>
+        <v>359.2716887303256</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>16.5</v>
+        <v>51</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.03485836985024</v>
+        <v>37.37738803334754</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>25.51557358846102</v>
+        <v>18.6515066601537</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.096303940648527</v>
+        <v>0.2888889938954439</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0601837276848102</v>
+        <v>-0.406700310518187</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>4960</v>
+        <v>6108</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>352.3676268049781</v>
+        <v>359.1587650020796</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.8</v>
+        <v>16.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>30.68041313502198</v>
+        <v>39.11834371386737</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>32.69511249004108</v>
+        <v>21.91953477863228</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4172714850854657</v>
+        <v>0.9009318776174722</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0225643201365759</v>
+        <v>-0.0727892752718297</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4989</v>
+        <v>4972</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>351.8421587589079</v>
+        <v>352.6943077243739</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>65.3</v>
+        <v>16.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.08274098551236</v>
+        <v>39.03485836985024</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>21.00124065248536</v>
+        <v>25.51557358846102</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2586417083614863</v>
+        <v>1.096303940648527</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.147569493183118</v>
+        <v>-0.0601837276848102</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>4958</v>
+        <v>4960</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>347.744493506857</v>
+        <v>352.3676268049781</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>470.5</v>
+        <v>20.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.13005128040453</v>
+        <v>30.68041313502198</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.4369380936222</v>
+        <v>32.69511249004108</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8881487411043562</v>
+        <v>0.4172714850854657</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-15.97174669895886</v>
+        <v>0.0225643201365759</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5351</v>
+        <v>4989</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>344.9233040864895</v>
+        <v>351.8421587589079</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.7219088736577</v>
+        <v>35.08274098551236</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.81875922924922</v>
+        <v>21.00124065248536</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5481631162397466</v>
+        <v>0.2586417083614863</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.320742927227032</v>
+        <v>-2.147569493183118</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>5299</v>
+        <v>4958</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>338.518434398357</v>
+        <v>347.744493506857</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>91</v>
+        <v>470.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.94266364121476</v>
+        <v>40.13005128040453</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.97954436412429</v>
+        <v>19.4369380936222</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3220610682604327</v>
+        <v>0.8881487411043562</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-2.968964680112413</v>
+        <v>-15.97174669895886</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6139</v>
+        <v>5351</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>335.5917980255045</v>
+        <v>344.9233040864895</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>762</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.25227602666113</v>
+        <v>44.7219088736577</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.55685667817735</v>
+        <v>13.81875922924922</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.959179802550454</v>
+        <v>0.5481631162397466</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-12.61579348342523</v>
+        <v>-1.320742927227032</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5292</v>
+        <v>5299</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>334.4212053535589</v>
+        <v>338.518434398357</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>166.5</v>
+        <v>91</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>30.04370934183295</v>
+        <v>35.94266364121476</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>30.30642110998246</v>
+        <v>27.97954436412429</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2720980364111889</v>
+        <v>0.3220610682604327</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-2.082942814818919</v>
+        <v>-2.968964680112413</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>4933</v>
+        <v>6139</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>331.7325110263358</v>
+        <v>335.5917980255045</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>55.7</v>
+        <v>762</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>29.10185380457357</v>
+        <v>41.25227602666113</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28.21508684375821</v>
+        <v>18.55685667817735</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6435563618804686</v>
+        <v>1.959179802550454</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.4620850417091757</v>
+        <v>-12.61579348342523</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>4968</v>
+        <v>5292</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>330.5394179666936</v>
+        <v>334.4212053535589</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>98</v>
+        <v>166.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>34.51898589965256</v>
+        <v>30.04370934183295</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.1460264154512</v>
+        <v>30.30642110998246</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6029322541826377</v>
+        <v>0.2720980364111889</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.043096359667437</v>
+        <v>-2.082942814818919</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>4974</v>
+        <v>4933</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>327.5543596466657</v>
+        <v>331.7325110263358</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.24697647284106</v>
+        <v>29.10185380457357</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>18.51053036083485</v>
+        <v>28.21508684375821</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8985448526166265</v>
+        <v>0.6435563618804686</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0039693511812419</v>
+        <v>-0.4620850417091757</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>5426</v>
+        <v>4968</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>326.4939451907855</v>
+        <v>330.5394179666936</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.1</v>
+        <v>98</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.05581409109793</v>
+        <v>34.51898589965256</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.14159436566037</v>
+        <v>23.1460264154512</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3858567648803042</v>
+        <v>0.6029322541826377</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.6154946647215506</v>
+        <v>-1.043096359667437</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4976</v>
+        <v>4974</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>324.8579953996033</v>
+        <v>327.5543596466657</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>33.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.2411169394052</v>
+        <v>42.24697647284106</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.52805754391705</v>
+        <v>18.51053036083485</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.54091041409937</v>
+        <v>0.8985448526166265</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.5691907373351681</v>
+        <v>-0.0039693511812419</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>5274</v>
+        <v>5426</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>319.3175449490875</v>
+        <v>326.4939451907855</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14695</v>
+        <v>25.1</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.31425914531897</v>
+        <v>38.05581409109793</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.40305505675195</v>
+        <v>20.14159436566037</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4369812900245372</v>
+        <v>0.3858567648803042</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>166.3848378113743</v>
+        <v>-0.6154946647215506</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>4526</v>
+        <v>4976</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>東台</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>319.2078530957729</v>
+        <v>324.8579953996033</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>30.65851172446878</v>
+        <v>47.2411169394052</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>32.11555284806516</v>
+        <v>19.52805754391705</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4291718405847085</v>
+        <v>1.54091041409937</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.6647178686245958</v>
+        <v>-0.5691907373351681</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4906</v>
+        <v>5274</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>317.659624768372</v>
+        <v>319.3175449490875</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>34.05</v>
+        <v>14695</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.33270747367473</v>
+        <v>46.31425914531897</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.54280510862002</v>
+        <v>18.40305505675195</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4255166076790571</v>
+        <v>0.4369812900245372</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.4258683808154346</v>
+        <v>166.3848378113743</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>4438</v>
+        <v>4526</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>廣越</t>
+          <t>東台</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>317.3963212584809</v>
+        <v>319.2078530957729</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>61.1</v>
+        <v>30.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.37601124552619</v>
+        <v>30.65851172446878</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.53989632852834</v>
+        <v>32.11555284806516</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3200310975001182</v>
+        <v>0.4291718405847085</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0850168375012663</v>
+        <v>-0.6647178686245958</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6138</v>
+        <v>4906</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>314.8311588694382</v>
+        <v>317.659624768372</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>318</v>
+        <v>34.05</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.4161912070272</v>
+        <v>35.33270747367473</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.04763031111252</v>
+        <v>24.54280510862002</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3466455227131261</v>
+        <v>0.4255166076790571</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-5.375533297565934</v>
+        <v>-0.4258683808154346</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>5345</v>
+        <v>4438</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>廣越</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>313.0291719260647</v>
+        <v>317.3963212584809</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>25.3</v>
+        <v>61.1</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.6320564384542</v>
+        <v>51.37601124552619</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.77943747571086</v>
+        <v>17.53989632852834</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.179106443988065</v>
+        <v>0.3200310975001182</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.3431323335474754</v>
+        <v>-0.0850168375012663</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>4916</v>
+        <v>6138</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>312.7551267054922</v>
+        <v>314.8311588694382</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.81581583971408</v>
+        <v>45.4161912070272</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.40626817142341</v>
+        <v>19.04763031111252</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2317306126521891</v>
+        <v>0.3466455227131261</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-1.279681101891408</v>
+        <v>-5.375533297565934</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6126</v>
+        <v>5345</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>信音</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>312.320540280598</v>
+        <v>313.0291719260647</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>30.8</v>
+        <v>25.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>36.87122907319449</v>
+        <v>51.6320564384542</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>30.01382588896035</v>
+        <v>14.77943747571086</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3096911973095194</v>
+        <v>1.179106443988065</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2282694339933006</v>
+        <v>0.3431323335474754</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5468</v>
+        <v>4916</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>凱鈺</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>309.6420912704963</v>
+        <v>312.7551267054922</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25.4</v>
+        <v>102</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.48474444625421</v>
+        <v>46.81581583971408</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.51985419144348</v>
+        <v>16.40626817142341</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5313610233945145</v>
+        <v>0.2317306126521891</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.698669254963433</v>
+        <v>-1.279681101891408</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4903</v>
+        <v>6126</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>信音</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>308.8650092934625</v>
+        <v>312.320540280598</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>38.8</v>
+        <v>30.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.8501463392427</v>
+        <v>36.87122907319449</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.37697249287292</v>
+        <v>30.01382588896035</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>2.033993692928927</v>
+        <v>0.3096911973095194</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>1</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1757552689843891</v>
+        <v>-0.2282694339933006</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>4554</v>
+        <v>5468</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>凱鈺</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>308.1586956870667</v>
+        <v>309.6420912704963</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>30.75</v>
+        <v>25.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46.05080148994056</v>
+        <v>47.48474444625421</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>23.68345213101085</v>
+        <v>18.51985419144348</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4540702727383309</v>
+        <v>0.5313610233945145</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1101676183938629</v>
+        <v>-0.698669254963433</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>5344</v>
+        <v>4903</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>307.0901399122017</v>
+        <v>308.8650092934625</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>14.7</v>
+        <v>38.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.24853710541656</v>
+        <v>49.8501463392427</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.04037886739654</v>
+        <v>16.37697249287292</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.0240079610398808</v>
+        <v>2.033993692928927</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1444837669128983</v>
+        <v>0.1757552689843891</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>5220</v>
+        <v>4554</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>306.4349764402506</v>
+        <v>308.1586956870667</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>20.8</v>
+        <v>30.75</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.43941933560006</v>
+        <v>46.05080148994056</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.62631735232881</v>
+        <v>23.68345213101085</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6519876387133025</v>
+        <v>0.4540702727383309</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0469260544394133</v>
+        <v>-0.1101676183938629</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>5386</v>
+        <v>5344</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>305.4845357262953</v>
+        <v>307.0901399122017</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>248</v>
+        <v>14.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>29.93533171526511</v>
+        <v>40.24853710541656</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.55973929756893</v>
+        <v>15.04037886739654</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4020935536344666</v>
+        <v>0.0240079610398808</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-11.93562880550214</v>
+        <v>-0.1444837669128983</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6161</v>
+        <v>5220</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>304.8755727509027</v>
+        <v>306.4349764402506</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>50.4</v>
+        <v>20.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.10468489153443</v>
+        <v>44.43941933560006</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.02223051806415</v>
+        <v>17.62631735232881</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4810986489527245</v>
+        <v>0.6519876387133025</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.2673815275673871</v>
+        <v>0.0469260544394133</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>5215</v>
+        <v>5386</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>302.7597279801951</v>
+        <v>305.4845357262953</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>38.4</v>
+        <v>248</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>32.63767212329832</v>
+        <v>29.93533171526511</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>25.15443787096985</v>
+        <v>24.55973929756893</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4702846690784563</v>
+        <v>0.4020935536344666</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.349422456675581</v>
+        <v>-11.93562880550214</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>5381</v>
+        <v>6161</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>302.0365714090617</v>
+        <v>304.8755727509027</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>23.6</v>
+        <v>50.4</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.63994233296953</v>
+        <v>46.10468489153443</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>25.11336703580052</v>
+        <v>14.02223051806415</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.2467091425497013</v>
+        <v>0.4810986489527245</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.3352043545764345</v>
+        <v>-0.2673815275673871</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4577</v>
+        <v>5534</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>長虹</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>301.7146715774894</v>
+        <v>303.0136399807359</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>70.3</v>
+        <v>79.3</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>32.73857780296663</v>
+        <v>47.65504161598663</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>28.51948096087853</v>
+        <v>14.38738421763616</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.372694448878377</v>
+        <v>0.4703764064587012</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0761303792211292</v>
+        <v>-0.131275575850772</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5469</v>
+        <v>5215</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>299.9338506348552</v>
+        <v>302.7597279801951</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>35.35504564039219</v>
+        <v>32.63767212329832</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>30.70964379989222</v>
+        <v>25.15443787096985</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.2110081320985554</v>
+        <v>0.4702846690784563</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.6656664955821787</v>
+        <v>-0.349422456675581</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>4991</v>
+        <v>5381</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>298.3535720002498</v>
+        <v>302.0365714090617</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>433.5</v>
+        <v>23.6</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>44.06109511648673</v>
+        <v>36.63994233296953</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>34.14786833599354</v>
+        <v>25.11336703580052</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.388545362261321</v>
+        <v>0.2467091425497013</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>5.335038147729307</v>
+        <v>-0.3352043545764345</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4739</v>
+        <v>4577</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>康普</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>296.779763035761</v>
+        <v>301.7146715774894</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>81.8</v>
+        <v>70.3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>32.11020943051058</v>
+        <v>32.73857780296663</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>32.74886077824283</v>
+        <v>28.51948096087853</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.3279388969070855</v>
+        <v>0.372694448878377</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.607542320610901</v>
+        <v>-0.0761303792211292</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>5258</v>
+        <v>5469</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>296.630882870159</v>
+        <v>299.9338506348552</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>52.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>50.70426491146702</v>
+        <v>35.35504564039219</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>12.09223588969543</v>
+        <v>30.70964379989222</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5772300521808158</v>
+        <v>0.2110081320985554</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.0262589743269228</v>
+        <v>-0.6656664955821787</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>4590</v>
+        <v>4991</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>富田-創</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>294.5878415478443</v>
+        <v>298.3535720002498</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>83.5</v>
+        <v>433.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46.22195404354714</v>
+        <v>44.06109511648673</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.20657794667585</v>
+        <v>34.14786833599354</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.4689412309426443</v>
+        <v>1.388545362261321</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-1.241444438503624</v>
+        <v>5.335038147729307</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>5230</v>
+        <v>4739</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>康普</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>294.0159553701003</v>
+        <v>296.779763035761</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>18.2</v>
+        <v>81.8</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>41.99878137699967</v>
+        <v>32.11020943051058</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>22.91735526532995</v>
+        <v>32.74886077824283</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.1988657646053352</v>
+        <v>0.3279388969070855</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.2999216970687774</v>
+        <v>-1.607542320610901</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>5493</v>
+        <v>5258</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>292.6641742718493</v>
+        <v>296.630882870159</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>33.71717914003693</v>
+        <v>50.70426491146702</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>22.14079779710299</v>
+        <v>12.09223588969543</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.3372156707777847</v>
+        <v>0.5772300521808158</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.6191733006765689</v>
+        <v>0.0262589743269228</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>5289</v>
+        <v>4590</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>富田-創</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>292.5152212762783</v>
+        <v>294.5878415478443</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>1330</v>
+        <v>83.5</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>38.14672405257652</v>
+        <v>46.22195404354714</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>31.61564994938333</v>
+        <v>19.20657794667585</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.7696293079874323</v>
+        <v>0.4689412309426443</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-8.551476654084766</v>
+        <v>-1.241444438503624</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>5223</v>
+        <v>5230</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>288.8594194013256</v>
+        <v>294.0159553701003</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>38.88070468171348</v>
+        <v>41.99878137699967</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>29.81464619825228</v>
+        <v>22.91735526532995</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.2318169385607461</v>
+        <v>0.1988657646053352</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.1479175269135476</v>
+        <v>-0.2999216970687774</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5347</v>
+        <v>5493</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>285.1815335419006</v>
+        <v>292.6641742718493</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>157</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,49 +7707,49 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>41.79946959879697</v>
+        <v>33.71717914003693</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>16.95130898542688</v>
+        <v>22.14079779710299</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.5318155495050283</v>
+        <v>0.3372156707777847</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-3.271822047321439</v>
+        <v>-0.6191733006765689</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5236</v>
+        <v>5289</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>285.1435936167388</v>
+        <v>292.5152212762783</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>148</v>
+        <v>1330</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>36.95943688069295</v>
+        <v>38.14672405257652</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>30.57249583020941</v>
+        <v>31.61564994938333</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5349189022228618</v>
+        <v>0.7696293079874323</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.7568418151853411</v>
+        <v>-8.551476654084766</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>4532</v>
+        <v>5223</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>瑞智</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>284.8711192680645</v>
+        <v>288.8594194013256</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>41.56385178480814</v>
+        <v>38.88070468171348</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>19.80933335030767</v>
+        <v>29.81464619825228</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.1952601952906005</v>
+        <v>0.2318169385607461</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.3109877808369856</v>
+        <v>-0.1479175269135476</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>4967</v>
+        <v>5347</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>284.2322336543722</v>
+        <v>285.1815335419006</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>223.5</v>
+        <v>157</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,49 +7866,49 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>39.31884389278747</v>
+        <v>41.79946959879697</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>30.75420263083405</v>
+        <v>16.95130898542688</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.6022170189151135</v>
+        <v>0.5318155495050283</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.1199684165653529</v>
+        <v>-3.271822047321439</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>4951</v>
+        <v>5236</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>282.9023073614314</v>
+        <v>285.1435936167388</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>80.7</v>
+        <v>148</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>33.96711830355369</v>
+        <v>36.95943688069295</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>39.4180986519456</v>
+        <v>30.57249583020941</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.7062231221231825</v>
+        <v>0.5349189022228618</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.2123780287379171</v>
+        <v>-0.7568418151853411</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>4770</v>
+        <v>4532</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>上品</t>
+          <t>瑞智</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>281.2104205953905</v>
+        <v>284.8711192680645</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>223</v>
+        <v>24.4</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>51.64407198144288</v>
+        <v>41.56385178480814</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>13.84624316202328</v>
+        <v>19.80933335030767</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.6906585440741886</v>
+        <v>0.1952601952906005</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>1.522317279129854</v>
+        <v>-0.3109877808369856</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>5355</v>
+        <v>4967</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>280.9440095208314</v>
+        <v>284.2322336543722</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>6.03</v>
+        <v>223.5</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>44.90665481716115</v>
+        <v>39.31884389278747</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>9.879434107877991</v>
+        <v>30.75420263083405</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.2679062471604903</v>
+        <v>0.6022170189151135</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0060880822183498</v>
+        <v>-0.1199684165653529</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5356</v>
+        <v>4951</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>279.5680464664372</v>
+        <v>282.9023073614314</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>24.5</v>
+        <v>80.7</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>27.0629072737044</v>
+        <v>33.96711830355369</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>23.69543124513535</v>
+        <v>39.4180986519456</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.4704530493594859</v>
+        <v>0.7062231221231825</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.1369868206683882</v>
+        <v>0.2123780287379171</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>4585</v>
+        <v>4770</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>上品</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>278.4685276491089</v>
+        <v>281.2104205953905</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>302.5</v>
+        <v>223</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45.18457136274188</v>
+        <v>51.64407198144288</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>11.33701207709243</v>
+        <v>13.84624316202328</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.2670655843862859</v>
+        <v>0.6906585440741886</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.4801238213678065</v>
+        <v>1.522317279129854</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>5474</v>
+        <v>5355</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>278.2205255832355</v>
+        <v>280.9440095208314</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>146.5</v>
+        <v>6.03</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>38.47116278481025</v>
+        <v>44.90665481716115</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>22.16190102532456</v>
+        <v>9.879434107877991</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.4841715025912712</v>
+        <v>0.2679062471604903</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.7103843864393262</v>
+        <v>-0.0060880822183498</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>4973</v>
+        <v>5356</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>277.4697833908993</v>
+        <v>279.5680464664372</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>142.5</v>
+        <v>24.5</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>41.29139483184203</v>
+        <v>27.0629072737044</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>21.07641595794888</v>
+        <v>23.69543124513535</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.430645435817492</v>
+        <v>0.4704530493594859</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-2.393793879965325</v>
+        <v>-0.1369868206683882</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>5392</v>
+        <v>4585</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>277.0174131193465</v>
+        <v>278.4685276491089</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>40.25</v>
+        <v>302.5</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>37.34797007872111</v>
+        <v>45.18457136274188</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>19.50781900423741</v>
+        <v>11.33701207709243</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.3695156601782685</v>
+        <v>0.2670655843862859</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.6770894183770222</v>
+        <v>-0.4801238213678065</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>4909</v>
+        <v>5474</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>276.2585968902367</v>
+        <v>278.2205255832355</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>38.55</v>
+        <v>146.5</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>33.02161813317363</v>
+        <v>38.47116278481025</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>44.95866009583538</v>
+        <v>22.16190102532456</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.4836555206834905</v>
+        <v>0.4841715025912712</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L149" s="2" t="n">
         <v>0</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.064571712706881</v>
+        <v>-0.7103843864393262</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>4583</v>
+        <v>4973</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>廣穎</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>275.2115413024102</v>
+        <v>277.4697833908993</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>579</v>
+        <v>142.5</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>40.78049016735359</v>
+        <v>41.29139483184203</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>34.57178715897258</v>
+        <v>21.07641595794888</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5513244320449301</v>
+        <v>0.430645435817492</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,31 +8414,31 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.878448200510185</v>
+        <v>-2.393793879965325</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>5321</v>
+        <v>5392</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>美而快</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>274.7202964141517</v>
+        <v>277.0174131193465</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>55</v>
+        <v>40.25</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,16 +8449,16 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>51.24026077481867</v>
+        <v>37.34797007872111</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>19.56649766422827</v>
+        <v>19.50781900423741</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.730668941664035</v>
+        <v>0.3695156601782685</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.9963208690392524</v>
+        <v>-0.6770894183770222</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>5225</v>
+        <v>4909</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>274.0743986352619</v>
+        <v>276.2585968902367</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>72.8</v>
+        <v>38.55</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,16 +8502,16 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>49.96149297126428</v>
+        <v>33.02161813317363</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>15.59696159749508</v>
+        <v>44.95866009583538</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.4271984469026559</v>
+        <v>0.4836555206834905</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.0159258384469575</v>
+        <v>-0.064571712706881</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>4581</v>
+        <v>4583</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>光隆精密-KY</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>266.3748670218415</v>
+        <v>275.2115413024102</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>51.2</v>
+        <v>579</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,16 +8555,16 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>54.42672922106581</v>
+        <v>40.78049016735359</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>10.96098613425326</v>
+        <v>34.57178715897258</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.3159719890831677</v>
+        <v>0.5513244320449301</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
@@ -8573,31 +8573,31 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.0312082270143667</v>
+        <v>0.878448200510185</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>5443</v>
+        <v>5321</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>美而快</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>262.2869012581603</v>
+        <v>274.7202964141517</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>39.64974530774469</v>
+        <v>51.24026077481867</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>23.90932225677625</v>
+        <v>19.56649766422827</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.2398689572096702</v>
+        <v>1.730668941664035</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.8690450708766244</v>
+        <v>-0.9963208690392524</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>5245</v>
+        <v>5225</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>262.2572792229919</v>
+        <v>274.0743986352619</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>23.45</v>
+        <v>72.8</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>33.98487871033412</v>
+        <v>49.96149297126428</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>16.57864719820969</v>
+        <v>15.59696159749508</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5067746036406076</v>
+        <v>0.4271984469026559</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.2271450773790019</v>
+        <v>0.0159258384469575</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>6104</v>
+        <v>4581</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>光隆精密-KY</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>261.2504255256498</v>
+        <v>266.3748670218415</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>92.8</v>
+        <v>51.2</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>40.52677545294976</v>
+        <v>54.42672922106581</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>18.17317793780487</v>
+        <v>10.96098613425326</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.278876174555083</v>
+        <v>0.3159719890831677</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.7855609388372726</v>
+        <v>-0.0312082270143667</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>4905</v>
+        <v>5443</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>259.2518463887158</v>
+        <v>262.2869012581603</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>50.95349613603935</v>
+        <v>39.64974530774469</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>11.65696829694357</v>
+        <v>23.90932225677625</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.5738500725308113</v>
+        <v>0.2398689572096702</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.0990034036973779</v>
+        <v>-0.8690450708766244</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>5432</v>
+        <v>5245</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>259.1391677004202</v>
+        <v>262.2572792229919</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>117</v>
+        <v>23.45</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>28.07616681782822</v>
+        <v>33.98487871033412</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>31.36274700742077</v>
+        <v>16.57864719820969</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.2838002373028828</v>
+        <v>0.5067746036406076</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>0</v>
@@ -8838,31 +8838,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-2.523620076088854</v>
+        <v>-0.2271450773790019</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>4961</v>
+        <v>6104</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>257.6834651159208</v>
+        <v>261.2504255256498</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>159</v>
+        <v>92.8</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>42.53561434712057</v>
+        <v>40.52677545294976</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>17.17814123032004</v>
+        <v>18.17317793780487</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.2859886939679065</v>
+        <v>0.278876174555083</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.9501822643594112</v>
+        <v>-0.7855609388372726</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>4729</v>
+        <v>5525</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>順天</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>257.0863355276617</v>
+        <v>261.0608882590743</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>19.6</v>
+        <v>22.85</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,16 +8926,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>41.71298367331348</v>
+        <v>57.86044329753456</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>20.85474162372388</v>
+        <v>19.60491626651109</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.4755025674058319</v>
+        <v>0.8783632479704598</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.1081124489463402</v>
+        <v>0.1346563999285144</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>6129</v>
+        <v>4905</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>普誠</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>256.8750876654706</v>
+        <v>259.2518463887158</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>14.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,13 +8979,13 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>36.07143444873631</v>
+        <v>50.95349613603935</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>26.16129263097051</v>
+        <v>11.65696829694357</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.2805604983962296</v>
+        <v>0.5738500725308113</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.4070821007872934</v>
+        <v>0.0990034036973779</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>4545</v>
+        <v>5432</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>255.7618577787476</v>
+        <v>259.1391677004202</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>33.6</v>
+        <v>117</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,13 +9032,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>40.58429296118858</v>
+        <v>28.07616681782822</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>23.38386338433385</v>
+        <v>31.36274700742077</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.2952552748930106</v>
+        <v>0.2838002373028828</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.3579763795330845</v>
+        <v>-2.523620076088854</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>4572</v>
+        <v>4961</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>駐龍</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>253.5767750001835</v>
+        <v>257.6834651159208</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>42.83684686909402</v>
+        <v>42.53561434712057</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>15.2693854700337</v>
+        <v>17.17814123032004</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.1727641384009877</v>
+        <v>0.2859886939679065</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.7550238135297105</v>
+        <v>-0.9501822643594112</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>4971</v>
+        <v>4729</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>253.2184958703797</v>
+        <v>257.0863355276617</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>433</v>
+        <v>19.6</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,13 +9138,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>44.32111947724556</v>
+        <v>41.71298367331348</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>29.44651146347247</v>
+        <v>20.85474162372388</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.247208979267774</v>
+        <v>0.4755025674058319</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>8.04933583559513</v>
+        <v>-0.1081124489463402</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>4924</v>
+        <v>6129</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>普誠</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>252.8237500057777</v>
+        <v>256.8750876654706</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>35.26936500603011</v>
+        <v>36.07143444873631</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>22.01772630807116</v>
+        <v>26.16129263097051</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.0689784419698453</v>
+        <v>0.2805604983962296</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.2374416356132837</v>
+        <v>-0.4070821007872934</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>4306</v>
+        <v>4545</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>炎洲</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>250.2458577454182</v>
+        <v>255.7618577787476</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>14.45</v>
+        <v>33.6</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>38.83359351696443</v>
+        <v>40.58429296118858</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>27.1272421940821</v>
+        <v>23.38386338433385</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.2969324844762929</v>
+        <v>0.2952552748930106</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.1324901699941431</v>
+        <v>-0.3579763795330845</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>6152</v>
+        <v>4572</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>駐龍</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>248.6128680031596</v>
+        <v>253.5767750001835</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>12.1</v>
+        <v>143</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,13 +9297,13 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>34.32101981706934</v>
+        <v>42.83684686909402</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>21.54409155762523</v>
+        <v>15.2693854700337</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.6450596196614901</v>
+        <v>0.1727641384009877</v>
       </c>
       <c r="K167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.0216423624833673</v>
+        <v>-0.7550238135297105</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>6123</v>
+        <v>4971</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>248.4292218425863</v>
+        <v>253.2184958703797</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>42.95</v>
+        <v>433</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>53.46216069871033</v>
+        <v>44.32111947724556</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>14.97192873255999</v>
+        <v>29.44651146347247</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.7688524239594545</v>
+        <v>1.247208979267774</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.2186799295236832</v>
+        <v>8.04933583559513</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>6125</v>
+        <v>4924</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>248.0987553741968</v>
+        <v>252.8237500057777</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>49.55</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,16 +9403,16 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>29.35984638336354</v>
+        <v>35.26936500603011</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>28.23024055632639</v>
+        <v>22.01772630807116</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.4778043937471156</v>
+        <v>0.0689784419698453</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>0</v>
@@ -9421,31 +9421,31 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.5446254130709578</v>
+        <v>-0.2374416356132837</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>5203</v>
+        <v>4306</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>炎洲</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>245.9628719606275</v>
+        <v>250.2458577454182</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>55.98505214866405</v>
+        <v>38.83359351696443</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>17.11768895133853</v>
+        <v>27.1272421940821</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.669877829325731</v>
+        <v>0.2969324844762929</v>
       </c>
       <c r="K170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.011030014821689</v>
+        <v>-0.1324901699941431</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>5251</v>
+        <v>6152</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>245.6172062229804</v>
+        <v>248.6128680031596</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>27.25</v>
+        <v>12.1</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,16 +9509,16 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>40.07281415050399</v>
+        <v>34.32101981706934</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>17.91972757769224</v>
+        <v>21.54409155762523</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.1998584900669915</v>
+        <v>0.6450596196614901</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.2322476290633879</v>
+        <v>-0.0216423624833673</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>5302</v>
+        <v>6123</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>240.8270952598039</v>
+        <v>248.4292218425863</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>10.3</v>
+        <v>42.95</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>35.80749991820333</v>
+        <v>53.46216069871033</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>26.29139445067706</v>
+        <v>14.97192873255999</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.3129247943146493</v>
+        <v>0.7688524239594545</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.3273152011704413</v>
+        <v>0.2186799295236832</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>4195</v>
+        <v>6125</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>基米-創</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>238.9073044845832</v>
+        <v>248.0987553741968</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>16.3</v>
+        <v>49.55</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>43.8525214510155</v>
+        <v>29.35984638336354</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>21.32067875275492</v>
+        <v>28.23024055632639</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.4148937277747454</v>
+        <v>0.4778043937471156</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.009188258919477599</v>
+        <v>-0.5446254130709578</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>6151</v>
+        <v>5203</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>晉倫</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>238.3241324803282</v>
+        <v>245.9628719606275</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>35.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,13 +9668,13 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>35.28164200245168</v>
+        <v>55.98505214866405</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>24.42335062429513</v>
+        <v>17.11768895133853</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.4213003143206107</v>
+        <v>1.669877829325731</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.188954081021913</v>
+        <v>-0.011030014821689</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>6112</v>
+        <v>5251</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>238.3151589388528</v>
+        <v>245.6172062229804</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>40.55</v>
+        <v>27.25</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>34.1769879839687</v>
+        <v>40.07281415050399</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>32.83924734960947</v>
+        <v>17.91972757769224</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.7249574578269246</v>
+        <v>0.1998584900669915</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,31 +9739,31 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.2529405776416276</v>
+        <v>-0.2322476290633879</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>6120</v>
+        <v>5302</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>238.2903312980609</v>
+        <v>240.8270952598039</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>12.6</v>
+        <v>10.3</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>38.27025863048459</v>
+        <v>35.80749991820333</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>12.9411572993698</v>
+        <v>26.29139445067706</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.210151571849719</v>
+        <v>0.3129247943146493</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.1316781844041992</v>
+        <v>-0.3273152011704413</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>4934</v>
+        <v>4195</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>基米-創</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>237.5096104565745</v>
+        <v>238.9073044845832</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>14.75</v>
+        <v>16.3</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,13 +9827,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>35.57426726859471</v>
+        <v>43.8525214510155</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>18.12917761947498</v>
+        <v>21.32067875275492</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.5959541229601062</v>
+        <v>0.4148937277747454</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.2054250279774604</v>
+        <v>0.009188258919477599</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>4569</v>
+        <v>6151</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>晉倫</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>234.0506016917441</v>
+        <v>238.3241324803282</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>157</v>
+        <v>35.8</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,16 +9880,16 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>39.23397809314254</v>
+        <v>35.28164200245168</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>17.4581112014944</v>
+        <v>24.42335062429513</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.8997422663764203</v>
+        <v>0.4213003143206107</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.9158939970091652</v>
+        <v>-0.188954081021913</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>亞元</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>231.5592531582241</v>
+        <v>238.3151589388528</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>11.9</v>
+        <v>40.55</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>44.90171597319091</v>
+        <v>34.1769879839687</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>17.91660897654511</v>
+        <v>32.83924734960947</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.1565353246063513</v>
+        <v>0.7249574578269246</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
@@ -9951,31 +9951,31 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.1575569288364217</v>
+        <v>-0.2529405776416276</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>4571</v>
+        <v>6120</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>鈞興-KY</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>231.0181831827931</v>
+        <v>238.2903312980609</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>153.5</v>
+        <v>12.6</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>36.90484520156603</v>
+        <v>38.27025863048459</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>30.91147824757794</v>
+        <v>12.9411572993698</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.2899780295929142</v>
+        <v>1.210151571849719</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>0</v>
@@ -10004,31 +10004,31 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.0395525219225803</v>
+        <v>-0.1316781844041992</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>6143</v>
+        <v>4934</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>振曜</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>228.7286444532058</v>
+        <v>237.5096104565745</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>93.8</v>
+        <v>14.75</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>42.77943747787143</v>
+        <v>35.57426726859471</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>18.65909217958757</v>
+        <v>18.12917761947498</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.2865275834550115</v>
+        <v>0.5959541229601062</v>
       </c>
       <c r="K181" s="2" t="n">
         <v>0</v>
@@ -10057,31 +10057,31 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-1.011497751862668</v>
+        <v>-0.2054250279774604</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>4737</v>
+        <v>4569</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>華廣</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>224.3618027680325</v>
+        <v>234.0506016917441</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>57.3</v>
+        <v>157</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10092,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>51.0550498139843</v>
+        <v>39.23397809314254</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>18.22642679415697</v>
+        <v>17.4581112014944</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.3083649664412993</v>
+        <v>0.8997422663764203</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L182" s="2" t="n">
         <v>0</v>
@@ -10110,31 +10110,31 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.1420574324145547</v>
+        <v>-0.9158939970091652</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>4555</v>
+        <v>6109</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>氣立</t>
+          <t>亞元</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>222.1036463617736</v>
+        <v>231.5592531582241</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>45.95</v>
+        <v>11.9</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,16 +10145,16 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>44.79683617651112</v>
+        <v>44.90171597319091</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>14.99685795655271</v>
+        <v>17.91660897654511</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.2994748789493682</v>
+        <v>0.1565353246063513</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.3106992117783133</v>
+        <v>-0.1575569288364217</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>5244</v>
+        <v>4571</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>鈞興-KY</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>221.2682159233288</v>
+        <v>231.0181831827931</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>32.1</v>
+        <v>153.5</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,13 +10198,13 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>33.06963959310909</v>
+        <v>36.90484520156603</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>36.04128252946929</v>
+        <v>30.91147824757794</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.3696995778609833</v>
+        <v>0.2899780295929142</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
@@ -10216,31 +10216,31 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.0067009801695518</v>
+        <v>-0.0395525219225803</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>4912</v>
+        <v>6143</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>振曜</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>218.2671964706959</v>
+        <v>228.7286444532058</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -10251,13 +10251,13 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>42.49469263822905</v>
+        <v>42.77943747787143</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>23.17584554985041</v>
+        <v>18.65909217958757</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.3292275832467852</v>
+        <v>0.2865275834550115</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.1502018031095868</v>
+        <v>-1.011497751862668</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>6115</v>
+        <v>4737</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>華廣</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>215.3262662978676</v>
+        <v>224.3618027680325</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>46</v>
+        <v>57.3</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,16 +10304,16 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>41.30930508172885</v>
+        <v>51.0550498139843</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>20.07085173422842</v>
+        <v>18.22642679415697</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.2645834088970582</v>
+        <v>0.3083649664412993</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L186" s="2" t="n">
         <v>0</v>
@@ -10322,31 +10322,31 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.0417442925882809</v>
+        <v>-0.1420574324145547</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>5315</v>
+        <v>4555</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>氣立</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>214.7820299812793</v>
+        <v>222.1036463617736</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>19.1</v>
+        <v>45.95</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,16 +10357,16 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>26.72817930886548</v>
+        <v>44.79683617651112</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>39.31415052402249</v>
+        <v>14.99685795655271</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.5764993477830005</v>
+        <v>0.2994748789493682</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L187" s="2" t="n">
         <v>0</v>
@@ -10375,31 +10375,31 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.081986287153966</v>
+        <v>-0.3106992117783133</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>4552</v>
+        <v>5244</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>力達-KY</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>207.0155900527341</v>
+        <v>221.2682159233288</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>18.5</v>
+        <v>32.1</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>28.69038630803391</v>
+        <v>33.06963959310909</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>25.9289751045125</v>
+        <v>36.04128252946929</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>2.507573374263214</v>
+        <v>0.3696995778609833</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
         <v>0</v>
@@ -10428,31 +10428,31 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.0711554368879269</v>
+        <v>-0.0067009801695518</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>4441</v>
+        <v>4912</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>195.9396648427459</v>
+        <v>218.2671964706959</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>175.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>35.35052064850457</v>
+        <v>42.49469263822905</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>23.05891446534971</v>
+        <v>23.17584554985041</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.4337817142522703</v>
+        <v>0.3292275832467852</v>
       </c>
       <c r="K189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.3323665638609645</v>
+        <v>0.1502018031095868</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>5465</v>
+        <v>6115</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>195.2487029981714</v>
+        <v>215.3262662978676</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>21.7</v>
+        <v>46</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>26.46301736472523</v>
+        <v>41.30930508172885</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>24.95175839792036</v>
+        <v>20.07085173422842</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.413893833106481</v>
+        <v>0.2645834088970582</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L190" s="2" t="n">
         <v>0</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.1990433609688292</v>
+        <v>-0.0417442925882809</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10544,21 +10544,21 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>5457</v>
+        <v>5315</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>194.2530286076738</v>
+        <v>214.7820299812793</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>30.15</v>
+        <v>19.1</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>39.06209082872441</v>
+        <v>26.72817930886548</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>19.40376154756154</v>
+        <v>39.31415052402249</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.7462387275136141</v>
+        <v>0.5764993477830005</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.2451441813200389</v>
+        <v>-0.081986287153966</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>5278</v>
+        <v>4552</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>力達-KY</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>190.0746716679758</v>
+        <v>207.0155900527341</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>23.85</v>
+        <v>18.5</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,16 +10622,16 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>45.21714939567659</v>
+        <v>28.69038630803391</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>13.22640440375022</v>
+        <v>25.9289751045125</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.2121114693544311</v>
+        <v>2.507573374263214</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.09859824368255719</v>
+        <v>-0.0711554368879269</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>5353</v>
+        <v>4441</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>189.5073055611135</v>
+        <v>195.9396648427459</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>28.5</v>
+        <v>175.5</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>43.83386606076728</v>
+        <v>35.35052064850457</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>29.38194788325203</v>
+        <v>23.05891446534971</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.5389436720529406</v>
+        <v>0.4337817142522703</v>
       </c>
       <c r="K193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.12343454282244</v>
+        <v>-0.3323665638609645</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>6113</v>
+        <v>5465</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>亞矽</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>179.7328967442498</v>
+        <v>195.2487029981714</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>36.56249379503465</v>
+        <v>26.46301736472523</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>19.91757135662928</v>
+        <v>24.95175839792036</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.2650521232059969</v>
+        <v>0.413893833106481</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>2</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.3168411160312776</v>
+        <v>-0.1990433609688292</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>5222</v>
+        <v>5457</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>176.0270299612321</v>
+        <v>194.2530286076738</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>115</v>
+        <v>30.15</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>41.59616917676198</v>
+        <v>39.06209082872441</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>13.9287648808041</v>
+        <v>19.40376154756154</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.3462526119452898</v>
+        <v>0.7462387275136141</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.9144981821000102</v>
+        <v>-0.2451441813200389</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>5272</v>
+        <v>5278</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>172.1478488610457</v>
+        <v>190.0746716679758</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>18.3</v>
+        <v>23.85</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,16 +10834,16 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>33.54209999151659</v>
+        <v>45.21714939567659</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>21.34357424802359</v>
+        <v>13.22640440375022</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.5093007212481289</v>
+        <v>0.2121114693544311</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.1140321830585198</v>
+        <v>-0.09859824368255719</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>6117</v>
+        <v>5353</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>171.2430490334042</v>
+        <v>189.5073055611135</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>68.3</v>
+        <v>28.5</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>38.47448415120213</v>
+        <v>43.83386606076728</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>29.85474067014515</v>
+        <v>29.38194788325203</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.8930708923574503</v>
+        <v>0.5389436720529406</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.1974479705266376</v>
+        <v>-0.12343454282244</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>4999</v>
+        <v>5519</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>164.523350547078</v>
+        <v>185.4909161930796</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>19.35</v>
+        <v>27.95</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>39.05679629617315</v>
+        <v>23.6790875573008</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>18.36831957679967</v>
+        <v>41.59510927490906</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.5123160933751877</v>
+        <v>0.4800307849013114</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.0335472272559226</v>
+        <v>-0.3061772477730768</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>4414</v>
+        <v>6113</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>如興</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>164.2640128806631</v>
+        <v>179.7328967442498</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>8.58</v>
+        <v>22.6</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,16 +10993,16 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>49.23852664183097</v>
+        <v>36.56249379503465</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>13.56850726097403</v>
+        <v>19.91757135662928</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.3086621330235922</v>
+        <v>0.2650521232059969</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0017676756503666</v>
+        <v>-0.3168411160312776</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>4426</v>
+        <v>5521</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>利勤</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>163.8228078114559</v>
+        <v>178.5799174299479</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>8.31</v>
+        <v>10.3</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,16 +11046,16 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>52.17236224441532</v>
+        <v>48.48264686113551</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>16.48786712592577</v>
+        <v>15.96190532200762</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.2131978625407097</v>
+        <v>0.4363646681061857</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L200" s="2" t="n">
         <v>0</v>
@@ -11064,31 +11064,31 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0057726037235091</v>
+        <v>0.008968985952516301</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>4935</v>
+        <v>5222</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>162.2649889810672</v>
+        <v>176.0270299612321</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>35.45</v>
+        <v>115</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>42.43220180371222</v>
+        <v>41.59616917676198</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>20.89821286959107</v>
+        <v>13.9287648808041</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.3196566886798819</v>
+        <v>0.3462526119452898</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.0176240695266491</v>
+        <v>-0.9144981821000102</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>4588</v>
+        <v>5272</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>160.5442494904471</v>
+        <v>172.1478488610457</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>51.4</v>
+        <v>18.3</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>34.26807828389975</v>
+        <v>33.54209999151659</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>17.64563054188313</v>
+        <v>21.34357424802359</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.2736122444656714</v>
+        <v>0.5093007212481289</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.4935429734301633</v>
+        <v>-0.1140321830585198</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>6158</v>
+        <v>6117</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>禾昌</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>158.9487739420863</v>
+        <v>171.2430490334042</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>17.9</v>
+        <v>68.3</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,16 +11205,16 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>44.66073146656203</v>
+        <v>38.47448415120213</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>20.71349006359777</v>
+        <v>29.85474067014515</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.6861404518214225</v>
+        <v>0.8930708923574503</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.09692112982384619</v>
+        <v>0.1974479705266376</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>6150</v>
+        <v>4999</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>撼訊</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>158.9043585501923</v>
+        <v>164.523350547078</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>55.3</v>
+        <v>19.35</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,16 +11258,16 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>35.99922867801473</v>
+        <v>39.05679629617315</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>20.65750508888077</v>
+        <v>18.36831957679967</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>1.030458545137159</v>
+        <v>0.5123160933751877</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.3745317807041306</v>
+        <v>-0.0335472272559226</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>6128</v>
+        <v>4414</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>如興</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>153.946018452093</v>
+        <v>164.2640128806631</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>20.2</v>
+        <v>8.58</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,16 +11311,16 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>47.19617300418803</v>
+        <v>49.23852664183097</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>13.1498783760514</v>
+        <v>13.56850726097403</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.4273639471879242</v>
+        <v>0.3086621330235922</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>0</v>
@@ -11329,31 +11329,31 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0108368604912574</v>
+        <v>-0.0017676756503666</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>4440</v>
+        <v>4426</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>利勤</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>151.288078077989</v>
+        <v>163.8228078114559</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>17.45</v>
+        <v>8.31</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,16 +11364,16 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>49.03523166819778</v>
+        <v>52.17236224441532</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>16.23123180227937</v>
+        <v>16.48786712592577</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.0621857683311242</v>
+        <v>0.2131978625407097</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.007758047072883</v>
+        <v>-0.0057726037235091</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>6124</v>
+        <v>4935</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>142.5371454358659</v>
+        <v>162.2649889810672</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>25.9</v>
+        <v>35.45</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,16 +11417,16 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>33.6205587273935</v>
+        <v>42.43220180371222</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>23.45916033576015</v>
+        <v>20.89821286959107</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.8076966468936115</v>
+        <v>0.3196566886798819</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>0</v>
@@ -11435,31 +11435,31 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.1580345330432409</v>
+        <v>0.0176240695266491</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>5283</v>
+        <v>4588</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>禾聯碩</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>140.5036570218739</v>
+        <v>160.5442494904471</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>53.2</v>
+        <v>51.4</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>48.95179241117255</v>
+        <v>34.26807828389975</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>13.75547955409238</v>
+        <v>17.64563054188313</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.7148553252488496</v>
+        <v>0.2736122444656714</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
@@ -11488,31 +11488,31 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.06452802890613769</v>
+        <v>-0.4935429734301633</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>4943</v>
+        <v>6158</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>禾昌</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>133.845165681531</v>
+        <v>158.9487739420863</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -11523,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>49.85606046304895</v>
+        <v>44.66073146656203</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>10.18875469989146</v>
+        <v>20.71349006359777</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.1192520223978258</v>
+        <v>0.6861404518214225</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" s="2" t="n">
         <v>0</v>
@@ -11541,31 +11541,31 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0356223895358926</v>
+        <v>-0.09692112982384619</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>6114</v>
+        <v>6150</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>撼訊</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>126.1210905191348</v>
+        <v>158.9043585501923</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>27.7</v>
+        <v>55.3</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -11576,16 +11576,16 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>39.31333771138872</v>
+        <v>35.99922867801473</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>13.4575165552297</v>
+        <v>20.65750508888077</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.0371648000115407</v>
+        <v>1.030458545137159</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L210" s="2" t="n">
         <v>0</v>
@@ -11594,31 +11594,31 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.1762408098549891</v>
+        <v>-0.3745317807041306</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>5205</v>
+        <v>6128</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>122.2390579932888</v>
+        <v>153.946018452093</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>22.05</v>
+        <v>20.2</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,13 +11629,13 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>50.10770955265441</v>
+        <v>47.19617300418803</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>18.43343504623238</v>
+        <v>13.1498783760514</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.2180097886395099</v>
+        <v>0.4273639471879242</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.2791919649399982</v>
+        <v>-0.0108368604912574</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11657,21 +11657,21 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>5287</v>
+        <v>4440</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>108.5233802726348</v>
+        <v>151.288078077989</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>147</v>
+        <v>17.45</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,16 +11682,16 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>42.21138451832998</v>
+        <v>49.03523166819778</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>15.74758033393291</v>
+        <v>16.23123180227937</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.7192970518135311</v>
+        <v>0.0621857683311242</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>0</v>
@@ -11700,31 +11700,31 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.2487991926216779</v>
+        <v>-0.007758047072883</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>5438</v>
+        <v>6124</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>107.4875175794964</v>
+        <v>142.5371454358659</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>17.3</v>
+        <v>25.9</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,16 +11735,16 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>33.84138283410809</v>
+        <v>33.6205587273935</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>16.8707062496056</v>
+        <v>23.45916033576015</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.6262114595251949</v>
+        <v>0.8076966468936115</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L213" s="2" t="n">
         <v>0</v>
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.1488481843208845</v>
+        <v>-0.1580345330432409</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>4560</v>
+        <v>5283</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>強信-KY</t>
+          <t>禾聯碩</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>104.2291429507786</v>
+        <v>140.5036570218739</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>31.65</v>
+        <v>53.2</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,16 +11788,16 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>39.12274955561074</v>
+        <v>48.95179241117255</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>18.81328274206125</v>
+        <v>13.75547955409238</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.8693491397408541</v>
+        <v>0.7148553252488496</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" s="2" t="n">
         <v>0</v>
@@ -11806,31 +11806,31 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.2789378442191631</v>
+        <v>-0.06452802890613769</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>4942</v>
+        <v>4943</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>78.15820412427493</v>
+        <v>133.845165681531</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>37</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>45.31448853272297</v>
+        <v>49.85606046304895</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>16.10437330365406</v>
+        <v>10.18875469989146</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>1.063195848610191</v>
+        <v>0.1192520223978258</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.0347124688522231</v>
+        <v>0.0356223895358926</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>6118</v>
+        <v>6114</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>60.13673680297348</v>
+        <v>126.1210905191348</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>16.05</v>
+        <v>27.7</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,16 +11894,16 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>39.8702924507906</v>
+        <v>39.31333771138872</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>17.01026591692795</v>
+        <v>13.4575165552297</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.2092681969606385</v>
+        <v>0.0371648000115407</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L216" s="2" t="n">
         <v>0</v>
@@ -11912,31 +11912,31 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.041867815099376</v>
+        <v>-0.1762408098549891</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>4746</v>
+        <v>5205</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>57.11825310848829</v>
+        <v>122.2390579932888</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>51.6</v>
+        <v>22.05</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,13 +11947,13 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>44.15426031231839</v>
+        <v>50.10770955265441</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>13.71439049060985</v>
+        <v>18.43343504623238</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.3333547193545889</v>
+        <v>0.2180097886395099</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
@@ -11965,31 +11965,31 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.2925180840982292</v>
+        <v>0.2791919649399982</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>4562</v>
+        <v>5287</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>穎漢</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>21.21014179287995</v>
+        <v>108.5233802726348</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>31.2</v>
+        <v>147</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>36.83274060445269</v>
+        <v>42.21138451832998</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>15.0615967975003</v>
+        <v>15.74758033393291</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.2257791439097887</v>
+        <v>0.7192970518135311</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>1</v>
@@ -12018,62 +12018,433 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.0976356226362118</v>
+        <v>-0.2487991926216779</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
+        <v>5438</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>東友</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>107.4875175794964</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>33.84138283410809</v>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>16.8707062496056</v>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>0.6262114595251949</v>
+      </c>
+      <c r="K219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>-0.1488481843208845</v>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>4560</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>強信-KY</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>104.2291429507786</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>39.12274955561074</v>
+      </c>
+      <c r="I220" s="2" t="n">
+        <v>18.81328274206125</v>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v>0.8693491397408541</v>
+      </c>
+      <c r="K220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>-0.2789378442191631</v>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>5531</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>鄉林</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>84.68564773221505</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>42.20998435097089</v>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>16.95865968728361</v>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>0.7971901531055376</v>
+      </c>
+      <c r="K221" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>-0.0138212940167438</v>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>嘉彰</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>78.15820412427493</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>45.31448853272297</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>16.10437330365406</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>1.063195848610191</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>-0.0347124688522231</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>6118</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>建達</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>60.13673680297348</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>39.8702924507906</v>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>17.01026591692795</v>
+      </c>
+      <c r="J223" s="2" t="n">
+        <v>0.2092681969606385</v>
+      </c>
+      <c r="K223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>-0.041867815099376</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>4746</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>台耀</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>57.11825310848829</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>44.15426031231839</v>
+      </c>
+      <c r="I224" s="2" t="n">
+        <v>13.71439049060985</v>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>0.3333547193545889</v>
+      </c>
+      <c r="K224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>-0.2925180840982292</v>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>4562</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>穎漢</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>21.21014179287995</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>36.83274060445269</v>
+      </c>
+      <c r="I225" s="2" t="n">
+        <v>15.0615967975003</v>
+      </c>
+      <c r="J225" s="2" t="n">
+        <v>0.2257791439097887</v>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>-0.0976356226362118</v>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>6160</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>欣技</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D219" s="2" t="n">
+      <c r="C226" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D226" s="2" t="n">
         <v>6.252111292936661</v>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="E226" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H219" s="2" t="n">
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H226" s="2" t="n">
         <v>36.95460661659194</v>
       </c>
-      <c r="I219" s="2" t="n">
+      <c r="I226" s="2" t="n">
         <v>11.2718426416952</v>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="J226" s="2" t="n">
         <v>0.558640519130205</v>
       </c>
-      <c r="K219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N219" s="2" t="n">
+      <c r="K226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N226" s="2" t="n">
         <v>-0.07526850482184309</v>
       </c>
-      <c r="O219" s="2" t="inlineStr">
+      <c r="O226" s="2" t="inlineStr">
         <is>
           <t>avoid_chase</t>
         </is>
